--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>45985.52083333334</v>
+        <v>45985.375</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45985.54166666666</v>
+        <v>45985.52083333334</v>
       </c>
     </row>
     <row r="5">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45985.5625</v>
+        <v>45985.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45985.58333333334</v>
+        <v>45985.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
         <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45985.60416666666</v>
+        <v>45985.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45985.625</v>
+        <v>45985.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1971,10 +1971,10 @@
         <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,11 +2251,11 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45985.64583333334</v>
+        <v>45985.625</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45985.66666666666</v>
+        <v>45985.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>45985.6875</v>
+        <v>45985.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>45985.69791666666</v>
+        <v>45985.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>45985.70833333334</v>
+        <v>45985.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>45985.79166666666</v>
+        <v>45985.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>45985.83333333334</v>
+        <v>45985.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4069,116 +4069,235 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>45985.83333333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>1.71</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>3.35</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N32" t="n">
         <v>5</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AB32" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="3" t="n">
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>45985.875</v>
       </c>
     </row>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2090,10 +2090,10 @@
         <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2090,10 +2090,10 @@
         <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2209,10 +2209,10 @@
         <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>4.05</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4030,16 +4030,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.19</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="M25" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
         <v>2.9</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.19</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>2.9</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
         <v>1.55</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
         <v>1.55</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,14 +1016,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1025,34 +1025,34 @@
         <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
         <v>1.5</v>
@@ -1061,28 +1061,28 @@
         <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1144,40 +1144,40 @@
         <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA6" t="n">
         <v>2.05</v>
@@ -1186,22 +1186,22 @@
         <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1263,40 +1263,40 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
         <v>1.63</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1858,40 +1858,40 @@
         <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1900,22 +1900,22 @@
         <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2215,40 +2215,40 @@
         <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
         <v>1.95</v>
@@ -2257,22 +2257,22 @@
         <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3280,10 +3280,10 @@
         <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3399,11 +3399,11 @@
         <v>2.45</v>
       </c>
       <c r="M25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N25" t="n">
         <v>3</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>4.12</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="T4" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.06</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.91</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.06</v>
+        <v>3.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>6.9</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.38</v>
+        <v>6.06</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
         <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2334,40 +2334,40 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2376,22 +2376,22 @@
         <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>6.9</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.38</v>
+        <v>6.06</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.06</v>
+        <v>3.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4.68</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.68</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.42</v>
+        <v>2.31</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="M20" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="O20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.69</v>
+        <v>4.54</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
         <v>2.29</v>
@@ -2831,7 +2831,7 @@
         <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
@@ -2843,31 +2843,31 @@
         <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>2.88</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.32</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.16</v>
+        <v>3.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.54</v>
+        <v>2.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.57</v>
       </c>
-      <c r="V21" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3042,11 +3042,11 @@
         <v>2.45</v>
       </c>
       <c r="M22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N22" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>4.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>3.24</v>
+        <v>3.09</v>
       </c>
       <c r="U3" t="n">
         <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.06</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.91</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>4.12</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="U4" t="n">
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>3.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.06</v>
+        <v>3.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.38</v>
+        <v>6.06</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>2.05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
         <v>5.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
         <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
         <v>5.5</v>
@@ -1314,13 +1314,13 @@
         <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>4.68</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.65</v>
+        <v>6.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AD9" t="n">
         <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>4.68</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1885,13 +1885,13 @@
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
         <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1900,19 +1900,19 @@
         <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD12" t="n">
         <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
         <v>1.33</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
         <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2337,16 +2337,16 @@
         <v>3.57</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
         <v>2.93</v>
@@ -2355,19 +2355,19 @@
         <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2382,16 +2382,16 @@
         <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG16" t="n">
         <v>1.46</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.47</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.18</v>
+        <v>3.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.69</v>
+        <v>2.84</v>
       </c>
       <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.26</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.12</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.32</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="N20" t="n">
-        <v>4.32</v>
+        <v>4.47</v>
       </c>
       <c r="O20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.54</v>
+        <v>4.69</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
         <v>2.29</v>
@@ -2831,7 +2831,7 @@
         <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
@@ -2843,31 +2843,31 @@
         <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.56</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>4.32</v>
       </c>
       <c r="O21" t="n">
-        <v>3.42</v>
+        <v>2.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.84</v>
+        <v>4.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.35</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3524,40 +3524,40 @@
         <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA26" t="n">
         <v>2.15</v>
@@ -3566,22 +3566,22 @@
         <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3643,40 +3643,40 @@
         <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA27" t="n">
         <v>1.92</v>
@@ -3685,22 +3685,22 @@
         <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3762,40 +3762,40 @@
         <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
         <v>1.7</v>
@@ -3804,22 +3804,22 @@
         <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -787,22 +787,22 @@
         <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>4.19</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
         <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="U3" t="n">
         <v>1.32</v>
@@ -814,13 +814,13 @@
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
         <v>2.4</v>
@@ -832,13 +832,13 @@
         <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
         <v>1.84</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
         <v>1.33</v>
@@ -906,34 +906,34 @@
         <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
         <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
@@ -948,22 +948,22 @@
         <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
         <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1025,28 +1025,28 @@
         <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T5" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
@@ -1055,10 +1055,10 @@
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
         <v>2.05</v>
@@ -1067,10 +1067,10 @@
         <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
         <v>1.8</v>
@@ -1079,10 +1079,10 @@
         <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1165,13 +1165,13 @@
         <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
         <v>1.5</v>
@@ -1180,7 +1180,7 @@
         <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="AB6" t="n">
         <v>1.34</v>
@@ -1189,7 +1189,7 @@
         <v>6.06</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
         <v>2.31</v>
@@ -1201,7 +1201,7 @@
         <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1263,13 +1263,13 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.1</v>
+        <v>4.35</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
@@ -1281,10 +1281,10 @@
         <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1293,7 +1293,7 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
         <v>4.05</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
         <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>4.68</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="U8" t="n">
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.65</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
         <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.68</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.05</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.1</v>
+        <v>6.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1861,37 +1861,37 @@
         <v>3.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
         <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1900,19 +1900,19 @@
         <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
         <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
         <v>1.33</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2.25</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2215,13 +2215,13 @@
         <v>3.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
         <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
@@ -2230,16 +2230,16 @@
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
         <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
@@ -2248,7 +2248,7 @@
         <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
         <v>1.67</v>
@@ -2260,19 +2260,19 @@
         <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2334,40 +2334,40 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
         <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2379,16 +2379,16 @@
         <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.38</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.1</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="AA17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.46</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="M20" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="O20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.69</v>
+        <v>4.54</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
         <v>2.29</v>
@@ -2831,7 +2831,7 @@
         <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
@@ -2843,31 +2843,31 @@
         <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>2.88</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.32</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.16</v>
+        <v>3.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.54</v>
+        <v>2.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.57</v>
       </c>
-      <c r="V21" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3048,40 +3048,40 @@
         <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA22" t="n">
         <v>2.5</v>
@@ -3090,22 +3090,22 @@
         <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>2.37</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.34</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3399,70 +3399,70 @@
         <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
         <v>1.75</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,70 +3634,70 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
         <v>1.75</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4000,34 +4000,34 @@
         <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
         <v>1.37</v>
@@ -4042,22 +4042,22 @@
         <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4238,40 +4238,40 @@
         <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
         <v>2</v>
@@ -4280,22 +4280,22 @@
         <v>1.72</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4.68</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1495,13 +1495,13 @@
         <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
         <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1513,19 +1513,19 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
@@ -1534,13 +1534,13 @@
         <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
         <v>3</v>
@@ -1549,16 +1549,16 @@
         <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
         <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.95</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
         <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>1.34</v>
@@ -1754,7 +1754,7 @@
         <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
         <v>1.42</v>
@@ -1769,16 +1769,16 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
         <v>2.76</v>
@@ -1787,13 +1787,13 @@
         <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
         <v>1.4</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.98</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>4.47</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.69</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2691,10 +2691,10 @@
         <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
         <v>3.75</v>
@@ -2712,40 +2712,40 @@
         <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>5.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
         <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD19" t="n">
         <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AF19" t="n">
         <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
         <v>1.95</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.32</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>2.16</v>
+        <v>3.42</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.54</v>
+        <v>2.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.57</v>
       </c>
-      <c r="V20" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.3</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.5</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V22" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3161,70 +3161,70 @@
         <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.11</v>
+        <v>3.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
         <v>2.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
         <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD25" t="n">
         <v>1.13</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="M31" t="n">
         <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>3.57</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.66</v>
+        <v>2.86</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.4</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.86</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.06</v>
+        <v>3.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.95</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>4.72</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
         <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="M17" t="n">
         <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.29</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,40 +2920,40 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
@@ -2965,28 +2965,28 @@
         <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
         <v>2.4</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>4.33</v>
+        <v>3.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>4.11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V24" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
         <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.37</v>
       </c>
-      <c r="V26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z26" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
         <v>1.75</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,70 +3634,70 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
         <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
         <v>1.75</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="T28" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AH28" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC29" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="O3" t="n">
         <v>3.18</v>
@@ -793,28 +793,28 @@
         <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
         <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
         <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -823,28 +823,28 @@
         <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AD3" t="n">
         <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.96</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.72</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="U8" t="n">
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="AD8" t="n">
         <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
         <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.95</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O21" t="n">
-        <v>2.23</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.11</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3084,7 +3084,7 @@
         <v>2.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
         <v>1.5</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.45</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
         <v>3.12</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.11</v>
+        <v>4.19</v>
       </c>
       <c r="R24" t="n">
         <v>1.56</v>
@@ -3301,10 +3301,10 @@
         <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
         <v>10</v>
@@ -3313,34 +3313,34 @@
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
         <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
         <v>1.47</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="M25" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
         <v>3.18</v>
@@ -823,10 +823,10 @@
         <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>3.96</v>
@@ -912,19 +912,19 @@
         <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
         <v>7.8</v>
@@ -936,7 +936,7 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
         <v>2.9</v>
@@ -951,10 +951,10 @@
         <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AF4" t="n">
         <v>1.91</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>6.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.06</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.73</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.42</v>
+        <v>6.06</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1266,7 +1266,7 @@
         <v>2.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
         <v>4.35</v>
@@ -1284,7 +1284,7 @@
         <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1293,7 +1293,7 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
         <v>4.05</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
         <v>1.66</v>
       </c>
       <c r="AF7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH7" t="n">
         <v>2.07</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.14</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
         <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1861,13 +1861,13 @@
         <v>3.95</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
         <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
         <v>2.5</v>
@@ -1879,7 +1879,7 @@
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
@@ -1888,10 +1888,10 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1909,7 +1909,7 @@
         <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
         <v>1.38</v>
@@ -1977,19 +1977,19 @@
         <v>2.83</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="Q13" t="n">
         <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
         <v>2.41</v>
@@ -2028,10 +2028,10 @@
         <v>1.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
         <v>1.6</v>
@@ -2099,22 +2099,22 @@
         <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>2.97</v>
       </c>
       <c r="T14" t="n">
         <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
         <v>6.9</v>
@@ -2123,10 +2123,10 @@
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
         <v>3.24</v>
@@ -2141,7 +2141,7 @@
         <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
         <v>1.67</v>
@@ -2239,7 +2239,7 @@
         <v>5.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
@@ -2248,7 +2248,7 @@
         <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="AA15" t="n">
         <v>1.67</v>
@@ -2263,16 +2263,16 @@
         <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>2.19</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2334,40 +2334,40 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="P16" t="n">
         <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2382,7 +2382,7 @@
         <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
         <v>1.93</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>5.35</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
@@ -2608,28 +2608,28 @@
         <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
         <v>2.4</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
         <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
         <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
         <v>3.1</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AA20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.46</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.45</v>
+        <v>4.19</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
         <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.19</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AA24" t="n">
         <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3524,22 +3524,22 @@
         <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
         <v>1.33</v>
@@ -3548,16 +3548,16 @@
         <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA26" t="n">
         <v>2.15</v>
@@ -3572,7 +3572,7 @@
         <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
@@ -3643,7 +3643,7 @@
         <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
         <v>2.2</v>
@@ -3655,28 +3655,28 @@
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
         <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
         <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AA27" t="n">
         <v>1.92</v>
@@ -3688,19 +3688,19 @@
         <v>3.24</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4012,7 +4012,7 @@
         <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T30" t="n">
         <v>2.95</v>
@@ -4021,13 +4021,13 @@
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
         <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
         <v>1.37</v>
@@ -4045,7 +4045,7 @@
         <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
         <v>2.05</v>
@@ -4116,7 +4116,7 @@
         <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
         <v>2.5</v>
@@ -4134,13 +4134,13 @@
         <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
@@ -4149,28 +4149,28 @@
         <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.49</v>
+        <v>3.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
         <v>3.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
         <v>1.73</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG31" t="n">
         <v>1.3</v>
@@ -4241,34 +4241,34 @@
         <v>2.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
         <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
         <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
         <v>3</v>
@@ -4283,19 +4283,19 @@
         <v>3.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
         <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AC14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="AG15" t="n">
         <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
@@ -2489,28 +2489,28 @@
         <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
         <v>2.4</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
         <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.9</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.55</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>3.42</v>
+        <v>2.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.45</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.48</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>4.19</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
         <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="T28" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.96</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>4.72</v>
+        <v>2.68</v>
       </c>
       <c r="O10" t="n">
-        <v>2.17</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.05</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2459,10 +2459,10 @@
         <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
         <v>3.36</v>
@@ -2471,25 +2471,25 @@
         <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
         <v>4.95</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB17" t="n">
         <v>2.35</v>
@@ -2498,13 +2498,13 @@
         <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AG17" t="n">
         <v>1.21</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>2.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>2.43</v>
+        <v>3.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.1</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.46</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.3</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
         <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
         <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="AA22" t="n">
         <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.45</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.48</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3399,70 +3399,70 @@
         <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.36</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.49</v>
-      </c>
       <c r="V29" t="n">
-        <v>6.05</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.73</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>6.75</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>6.06</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1</v>
+        <v>6.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.06</v>
+        <v>3.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="AG14" t="n">
         <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>4.01</v>
       </c>
       <c r="O15" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
         <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="O17" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
         <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
@@ -2486,31 +2486,31 @@
         <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AE17" t="n">
         <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>4.54</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.37</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.09</v>
+        <v>1.46</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AA22" t="n">
         <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3277,25 +3277,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
         <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
         <v>2.75</v>
@@ -3304,7 +3304,7 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
         <v>8.4</v>
@@ -3316,28 +3316,28 @@
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="AD24" t="n">
         <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
         <v>1.33</v>
@@ -3405,25 +3405,25 @@
         <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="P25" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.19</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
         <v>10</v>
@@ -3438,7 +3438,7 @@
         <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AA25" t="n">
         <v>2.3</v>
@@ -3450,16 +3450,16 @@
         <v>5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
         <v>1.47</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.88</v>
+        <v>3.47</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.47</v>
+        <v>2.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3872,67 +3872,67 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
         <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
         <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.64</v>
+        <v>3.84</v>
       </c>
       <c r="AD29" t="n">
         <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG29" t="n">
         <v>1.33</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AF30" t="n">
         <v>1.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4229,43 +4229,43 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="O32" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P32" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
         <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
         <v>1.31</v>
@@ -4274,28 +4274,28 @@
         <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
         <v>1.91</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>6.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.06</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.73</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>2.89</v>
+        <v>3.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>6.75</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.42</v>
+        <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>4.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>6.9</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>4.01</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="P15" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AH15" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.78</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.32</v>
+        <v>2.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>4.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>2.23</v>
+        <v>2.98</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.54</v>
+        <v>3.64</v>
       </c>
       <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.25</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.11</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>4.54</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>2.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.21</v>
+        <v>3.32</v>
       </c>
       <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.11</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
         <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3399,70 +3399,70 @@
         <v>2.45</v>
       </c>
       <c r="M25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N25" t="n">
         <v>3</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
         <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.47</v>
+        <v>2.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.88</v>
+        <v>3.47</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>4.05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>2.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="T4" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.73</v>
+        <v>2.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.89</v>
+        <v>3.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>6.75</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>5.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>3.95</v>
+        <v>2.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>6.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.75</v>
+        <v>3.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1266,25 +1266,25 @@
         <v>2.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.35</v>
+        <v>5.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
         <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1296,7 +1296,7 @@
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
         <v>1.63</v>
@@ -1308,19 +1308,19 @@
         <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1858,13 +1858,13 @@
         <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.52</v>
@@ -1876,13 +1876,13 @@
         <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
         <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.08</v>
@@ -1906,16 +1906,16 @@
         <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>4.01</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AH13" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.96</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>4.01</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>5.25</v>
       </c>
       <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.04</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2334,40 +2334,40 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2379,16 +2379,16 @@
         <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
         <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
         <v>1.38</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.21</v>
+        <v>2.98</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.86</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.11</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.98</v>
+        <v>2.21</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>4.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.14</v>
+        <v>2.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>2.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.41</v>
+        <v>3.09</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>3.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3524,40 +3524,40 @@
         <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
         <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
         <v>2.15</v>
@@ -3566,7 +3566,7 @@
         <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AD26" t="n">
         <v>1.22</v>
@@ -3578,7 +3578,7 @@
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.75</v>
@@ -3771,31 +3771,31 @@
         <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
         <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
         <v>1.7</v>
@@ -3804,22 +3804,22 @@
         <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
         <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,70 +4110,70 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="M31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" t="n">
         <v>3.25</v>
       </c>
-      <c r="N31" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q31" t="n">
         <v>4.05</v>
       </c>
       <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.38</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V31" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
         <v>3.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
         <v>1.73</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
         <v>1.73</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -787,13 +787,13 @@
         <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -802,16 +802,16 @@
         <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1.08</v>
@@ -820,7 +820,7 @@
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AA3" t="n">
         <v>2.45</v>
@@ -829,13 +829,13 @@
         <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>1.8</v>
@@ -844,7 +844,7 @@
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -906,25 +906,25 @@
         <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
         <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
         <v>7.5</v>
@@ -936,7 +936,7 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
         <v>2.9</v>
@@ -954,7 +954,7 @@
         <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
         <v>1.91</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.95</v>
+        <v>2.83</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>2.69</v>
       </c>
       <c r="T5" t="n">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.4</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1263,10 +1263,10 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1278,13 +1278,13 @@
         <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
         <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>5.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="U8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>5.95</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,40 +1611,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.68</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
@@ -1653,31 +1653,31 @@
         <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA10" t="n">
         <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1873,25 +1873,25 @@
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1903,19 +1903,19 @@
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.37</v>
       </c>
       <c r="AG13" t="n">
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.01</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.3</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AD14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AC15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2334,40 +2334,40 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>3.59</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2379,16 +2379,16 @@
         <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
         <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.38</v>
@@ -2602,10 +2602,10 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AA18" t="n">
         <v>1.9</v>
@@ -2614,10 +2614,10 @@
         <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
         <v>1.68</v>
@@ -2626,7 +2626,7 @@
         <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
         <v>1.47</v>
@@ -3051,16 +3051,16 @@
         <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
         <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
@@ -3075,13 +3075,13 @@
         <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
         <v>2.2</v>
@@ -3090,16 +3090,16 @@
         <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.45</v>
+        <v>4.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.38</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
         <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD23" t="n">
         <v>1.13</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3280,70 +3280,70 @@
         <v>2.45</v>
       </c>
       <c r="M24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N24" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3530,34 +3530,34 @@
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="R26" t="n">
         <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
         <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
         <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
         <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
         <v>2.15</v>
@@ -3569,7 +3569,7 @@
         <v>3.86</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
         <v>1.91</v>
@@ -3581,7 +3581,7 @@
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3646,37 +3646,37 @@
         <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
         <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U27" t="n">
         <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="AA27" t="n">
         <v>1.92</v>
@@ -3685,13 +3685,13 @@
         <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
         <v>1.95</v>
@@ -3700,7 +3700,7 @@
         <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3771,31 +3771,31 @@
         <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
         <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
         <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
         <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="AA28" t="n">
         <v>1.7</v>
@@ -3804,22 +3804,22 @@
         <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD28" t="n">
         <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF28" t="n">
         <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
         <v>2.3</v>
@@ -4006,43 +4006,43 @@
         <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
         <v>7.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
         <v>1.22</v>
@@ -4054,10 +4054,10 @@
         <v>1.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>2.7</v>
@@ -4253,31 +4253,31 @@
         <v>2.59</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
         <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
         <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>3.8</v>
@@ -4289,13 +4289,13 @@
         <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
         <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
         <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
@@ -1635,49 +1635,49 @@
         <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="W10" t="n">
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>5.85</v>
+        <v>5.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.37</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
         <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
         <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="N19" t="n">
         <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.86</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.53</v>
       </c>
-      <c r="V19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="O20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
         <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
         <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.32</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>4.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
         <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>3.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V22" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
         <v>1.99</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.91</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.36</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.21</v>
-      </c>
       <c r="Z28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC28" t="n">
         <v>3.84</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AD28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.91</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q29" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V29" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,37 +4110,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="M31" t="n">
         <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="P31" t="n">
         <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
@@ -4170,13 +4170,13 @@
         <v>1.73</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
         <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
         <v>2.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="M6" t="n">
         <v>2.8</v>
@@ -1165,19 +1165,19 @@
         <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
         <v>2.95</v>
@@ -1192,7 +1192,7 @@
         <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
         <v>1.55</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.3</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.81</v>
+        <v>3.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>5.55</v>
+        <v>5.85</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>5.85</v>
+        <v>5.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
         <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>3.86</v>
       </c>
       <c r="O18" t="n">
-        <v>2.98</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>4.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
         <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>4.85</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
         <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
         <v>2.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.86</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.64</v>
+        <v>3.14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
         <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>4.85</v>
+        <v>5.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
         <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="R22" t="n">
         <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="V22" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
         <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>3.93</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.14</v>
+        <v>2.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>2.76</v>
       </c>
       <c r="T23" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.6</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE24" t="n">
         <v>1.99</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
         <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3441,7 +3441,7 @@
         <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
         <v>1.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>4.69</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.01</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.91</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1031,31 +1031,31 @@
         <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
         <v>2.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
         <v>6.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
         <v>3.12</v>
@@ -1070,7 +1070,7 @@
         <v>3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
         <v>1.8</v>
@@ -1079,10 +1079,10 @@
         <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
         <v>2.8</v>
@@ -1174,10 +1174,10 @@
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
         <v>2.95</v>
@@ -1263,10 +1263,10 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1278,10 +1278,10 @@
         <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
         <v>5.5</v>
@@ -1293,7 +1293,7 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
         <v>4.2</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.89</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.95</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1864,34 +1864,34 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
         <v>8</v>
       </c>
       <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1903,19 +1903,19 @@
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
         <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.31</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2129,31 +2129,31 @@
         <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.98</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.98</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.25</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,64 +2801,64 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>5.4</v>
+        <v>4.85</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
         <v>2.3</v>
@@ -2867,7 +2867,7 @@
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="M21" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.3</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="T21" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="U21" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
         <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
         <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AD22" t="n">
         <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.93</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="R24" t="n">
         <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
         <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD24" t="n">
         <v>1.13</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AG27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3881,13 +3881,13 @@
         <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
@@ -3896,10 +3896,10 @@
         <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
         <v>6</v>
@@ -3908,7 +3908,7 @@
         <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>1.21</v>
@@ -3923,22 +3923,22 @@
         <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD29" t="n">
         <v>1.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4113,34 +4113,34 @@
         <v>2.14</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
         <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.85</v>
+        <v>6.95</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
@@ -4167,16 +4167,16 @@
         <v>1.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.43</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="AD4" t="n">
         <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.45</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.08</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.02</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1254,19 +1254,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1278,10 +1278,10 @@
         <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
         <v>5.5</v>
@@ -1296,13 +1296,13 @@
         <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AC7" t="n">
         <v>2.62</v>
@@ -1317,10 +1317,10 @@
         <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>4.56</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.89</v>
+        <v>3.26</v>
       </c>
       <c r="T9" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>4.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
         <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="P15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.44</v>
       </c>
       <c r="U15" t="n">
         <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
         <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
         <v>3.55</v>
@@ -2382,16 +2382,16 @@
         <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
         <v>1.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
         <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,64 +2563,64 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="N18" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.64</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
         <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
         <v>2.4</v>
@@ -2629,7 +2629,7 @@
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>3.86</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>4.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
         <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
         <v>1.56</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,64 +2920,64 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4</v>
+        <v>4.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
         <v>2.3</v>
@@ -2986,7 +2986,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U24" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
         <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AD24" t="n">
         <v>1.13</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.69</v>
+        <v>3.95</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="W25" t="n">
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.91</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>3.26</v>
+        <v>2.66</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.84</v>
+        <v>2.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>2.28</v>
+        <v>2.73</v>
       </c>
       <c r="P29" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.95</v>
+        <v>4.56</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="T29" t="n">
-        <v>2.66</v>
+        <v>3.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>9.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
         <v>3.1</v>
@@ -793,25 +793,25 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
@@ -820,31 +820,31 @@
         <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
         <v>3.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>2.99</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.21</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.08</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1864,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
@@ -1873,16 +1873,16 @@
         <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
         <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
@@ -1891,28 +1891,28 @@
         <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
         <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
         <v>1.33</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
@@ -1986,13 +1986,13 @@
         <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
         <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
@@ -2001,7 +2001,7 @@
         <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2010,25 +2010,25 @@
         <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
         <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
         <v>1.31</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>2.54</v>
@@ -2102,58 +2102,58 @@
         <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
         <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
         <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
         <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>4.01</v>
       </c>
       <c r="O15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
@@ -2230,16 +2230,16 @@
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
         <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
@@ -2248,13 +2248,13 @@
         <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA15" t="n">
         <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
         <v>2.56</v>
@@ -2266,13 +2266,13 @@
         <v>1.59</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG15" t="n">
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,64 +2444,64 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.4</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.39</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.3</v>
@@ -2510,7 +2510,7 @@
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,64 +2563,64 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
         <v>2.4</v>
@@ -2629,7 +2629,7 @@
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2685,19 +2685,19 @@
         <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
         <v>2.98</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
         <v>1.38</v>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB19" t="n">
         <v>1.8</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>2.31</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="N20" t="n">
-        <v>3.86</v>
+        <v>2.69</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.64</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,64 +2920,64 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>2.3</v>
@@ -2986,7 +2986,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.95</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.96</v>
-      </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="AA24" t="n">
         <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="O25" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.95</v>
+        <v>3.23</v>
       </c>
       <c r="R25" t="n">
         <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
         <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="N27" t="n">
-        <v>3.53</v>
+        <v>3.97</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
         <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
         <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
         <v>1.36</v>
@@ -3780,28 +3780,28 @@
         <v>2.66</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
         <v>3.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
         <v>2.75</v>
@@ -3810,10 +3810,10 @@
         <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
         <v>1.25</v>
@@ -4113,10 +4113,10 @@
         <v>2.14</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>2.5</v>
@@ -4134,16 +4134,16 @@
         <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
@@ -4152,7 +4152,7 @@
         <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AA31" t="n">
         <v>1.97</v>
@@ -4167,16 +4167,16 @@
         <v>1.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF31" t="n">
         <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.95</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.6</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.35</v>
-      </c>
       <c r="O9" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
         <v>2.88</v>
       </c>
       <c r="N12" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1867,10 +1867,10 @@
         <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
         <v>3.34</v>
@@ -1879,22 +1879,22 @@
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.06</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
         <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
         <v>1.62</v>
@@ -1903,16 +1903,16 @@
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="n">
         <v>1.33</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
@@ -2254,19 +2254,19 @@
         <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
         <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
         <v>1.25</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.23</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.26</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.8</v>
+        <v>3.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="N18" t="n">
-        <v>3.79</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
         <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O19" t="n">
         <v>2.3</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.98</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.25</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.67</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.14</v>
+        <v>2.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
         <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,64 +2920,64 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.3</v>
       </c>
       <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.53</v>
       </c>
-      <c r="V21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
         <v>2.3</v>
@@ -2986,7 +2986,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>3.23</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.23</v>
+        <v>3.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.2</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.38</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AH26" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.56</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="T29" t="n">
         <v>3.24</v>
@@ -3902,25 +3902,25 @@
         <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
         <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
         <v>4.1</v>
@@ -3929,16 +3929,16 @@
         <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
         <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3991,43 +3991,43 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8</v>
+        <v>6.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
         <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
         <v>1.37</v>
@@ -4036,28 +4036,28 @@
         <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AD30" t="n">
         <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="R32" t="n">
         <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="T32" t="n">
         <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.9</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.23</v>
-      </c>
       <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.32</v>
       </c>
-      <c r="V3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.67</v>
+        <v>3.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.08</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>5.85</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.08</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>5.85</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.87</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
         <v>4.9</v>
@@ -2721,34 +2721,34 @@
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
         <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
         <v>4.9</v>
@@ -2840,34 +2840,34 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
         <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3084,10 +3084,10 @@
         <v>2.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.93</v>
       </c>
-      <c r="O24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="M25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.88</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.28</v>
-      </c>
       <c r="U25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.26</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.8</v>
       </c>
-      <c r="O26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AD26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="V26" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.2</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.38</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3991,25 +3991,25 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O30" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.24</v>
+        <v>5.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
         <v>2.62</v>
@@ -4024,19 +4024,19 @@
         <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
         <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB30" t="n">
         <v>1.71</v>
@@ -4045,7 +4045,7 @@
         <v>3.74</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
         <v>2.22</v>
@@ -4054,10 +4054,10 @@
         <v>1.64</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4113,19 +4113,19 @@
         <v>2.14</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="P31" t="n">
         <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.03</v>
+        <v>3.49</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
@@ -4134,28 +4134,28 @@
         <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
@@ -4164,7 +4164,7 @@
         <v>3.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
         <v>1.73</v>
@@ -4173,10 +4173,10 @@
         <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
         <v>2.75</v>
@@ -4244,13 +4244,13 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
         <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="T32" t="n">
         <v>3.04</v>
@@ -4262,7 +4262,7 @@
         <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
@@ -4271,31 +4271,31 @@
         <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="AA32" t="n">
         <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD32" t="n">
         <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
         <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
         <v>2.8</v>
@@ -1144,10 +1144,10 @@
         <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
         <v>4.5</v>
@@ -1156,7 +1156,7 @@
         <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
         <v>4</v>
@@ -1171,25 +1171,25 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
         <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
         <v>2.31</v>
@@ -1254,19 +1254,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1278,10 +1278,10 @@
         <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
         <v>5.5</v>
@@ -1290,19 +1290,19 @@
         <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
         <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>2.62</v>
@@ -1317,7 +1317,7 @@
         <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
         <v>2.14</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="O10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1894,10 +1894,10 @@
         <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
         <v>4.2</v>
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.08</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
         <v>4.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
         <v>5.85</v>
@@ -2129,7 +2129,7 @@
         <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
         <v>1.67</v>
@@ -2141,16 +2141,16 @@
         <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
         <v>1.91</v>
@@ -2325,70 +2325,70 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.8</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="AD16" t="n">
         <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
         <v>1.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.32</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.28</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O18" t="n">
         <v>2.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.98</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.25</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.67</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.14</v>
+        <v>2.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.79</v>
+        <v>4.33</v>
       </c>
       <c r="O19" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
         <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
         <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19" t="n">
         <v>1.51</v>
@@ -2733,22 +2733,22 @@
         <v>2.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
         <v>4.9</v>
@@ -2840,34 +2840,34 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="n">
         <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,64 +2920,64 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="N21" t="n">
-        <v>4.33</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF21" t="n">
         <v>2.3</v>
@@ -2986,7 +2986,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="M24" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.84</v>
+        <v>3.23</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="N25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.93</v>
       </c>
-      <c r="O25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3518,70 +3518,70 @@
         <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
         <v>2.48</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD26" t="n">
         <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3637,10 +3637,10 @@
         <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
         <v>2.75</v>
@@ -3679,10 +3679,10 @@
         <v>2.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>4.4</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="T28" t="n">
-        <v>2.66</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
         <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
         <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>3.09</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>2.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.02</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1263,10 +1263,10 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1281,7 +1281,7 @@
         <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
         <v>5.5</v>
@@ -1296,7 +1296,7 @@
         <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
         <v>1.63</v>
@@ -1308,7 +1308,7 @@
         <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
         <v>1.62</v>
@@ -1317,10 +1317,10 @@
         <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1873,7 +1873,7 @@
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
         <v>1.32</v>
@@ -1885,13 +1885,13 @@
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1903,16 +1903,16 @@
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
         <v>1.33</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,43 +1968,43 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.64</v>
+        <v>4.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>5.85</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.2</v>
@@ -2013,28 +2013,28 @@
         <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
         <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2206,31 +2206,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
         <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
         <v>1.38</v>
@@ -2239,37 +2239,37 @@
         <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
         <v>1.57</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.96</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>4.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,64 +2563,64 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
         <v>2.3</v>
       </c>
       <c r="U18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.53</v>
       </c>
-      <c r="V18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>2.3</v>
@@ -2629,7 +2629,7 @@
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>3.79</v>
       </c>
       <c r="O19" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
         <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
         <v>1.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.51</v>
@@ -2733,22 +2733,22 @@
         <v>2.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.79</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.26</v>
+        <v>3.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3054,28 +3054,28 @@
         <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
         <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="T22" t="n">
         <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
         <v>1.4</v>
@@ -3096,7 +3096,7 @@
         <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
         <v>1.85</v>
@@ -3105,7 +3105,7 @@
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AF24" t="n">
         <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="M25" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.76</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3643,34 +3643,34 @@
         <v>3.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
         <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="R27" t="n">
         <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
         <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
         <v>1.42</v>
@@ -3688,16 +3688,16 @@
         <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
         <v>1.75</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>8.9</v>
+        <v>5.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="P29" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>8.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3991,61 +3991,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
         <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
         <v>3.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V30" t="n">
         <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
         <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
         <v>3.74</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
         <v>2.22</v>
@@ -4054,10 +4054,10 @@
         <v>1.64</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>2.75</v>
@@ -4247,22 +4247,22 @@
         <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="T32" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
         <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
@@ -4271,13 +4271,13 @@
         <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>3.8</v>
@@ -4286,16 +4286,16 @@
         <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U3" t="n">
         <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.35</v>
+        <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.49</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="N10" t="n">
-        <v>4.75</v>
+        <v>2.31</v>
       </c>
       <c r="O10" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.08</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1754,31 +1754,31 @@
         <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U11" t="n">
         <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC11" t="n">
         <v>2.89</v>
@@ -1787,16 +1787,16 @@
         <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AG11" t="n">
         <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.37</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -2468,16 +2468,16 @@
         <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -2492,7 +2492,7 @@
         <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>2.55</v>
@@ -2501,7 +2501,7 @@
         <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
         <v>2.3</v>
@@ -2510,7 +2510,7 @@
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,46 +2563,46 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="N18" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
         <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
         <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
         <v>4.8</v>
@@ -2611,16 +2611,16 @@
         <v>1.51</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD18" t="n">
         <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>2.3</v>
@@ -2629,7 +2629,7 @@
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.79</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
         <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
         <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.3</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.28</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>8.9</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
         <v>3.3</v>
@@ -4119,13 +4119,13 @@
         <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="P31" t="n">
         <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.49</v>
+        <v>4.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
@@ -4134,7 +4134,7 @@
         <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
         <v>3.48</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
@@ -4164,7 +4164,7 @@
         <v>3.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
         <v>1.73</v>
@@ -4173,10 +4173,10 @@
         <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
         <v>3.1</v>
@@ -912,10 +912,10 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
@@ -924,43 +924,43 @@
         <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
         <v>2.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
         <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
         <v>1.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.76</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>2.31</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.85</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
         <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.37</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AG14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.4</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="O20" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.16</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF20" t="n">
         <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC21" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="M22" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="N23" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S23" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
         <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
         <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="N25" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.93</v>
+        <v>4.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
         <v>3.05</v>
@@ -811,16 +811,16 @@
         <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA3" t="n">
         <v>2.4</v>
@@ -829,19 +829,19 @@
         <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
         <v>1.3</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
         <v>3.1</v>
@@ -942,10 +942,10 @@
         <v>2.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
         <v>4.5</v>
@@ -1025,40 +1025,40 @@
         <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AA5" t="n">
         <v>2.05</v>
@@ -1070,19 +1070,19 @@
         <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
         <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1144,28 +1144,28 @@
         <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R6" t="n">
         <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U6" t="n">
         <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -1186,22 +1186,22 @@
         <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AD6" t="n">
         <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AF6" t="n">
         <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1266,7 +1266,7 @@
         <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1278,10 +1278,10 @@
         <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
         <v>5.5</v>
@@ -1296,7 +1296,7 @@
         <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
         <v>1.63</v>
@@ -1308,7 +1308,7 @@
         <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
         <v>1.62</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
         <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
         <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1864,34 +1864,34 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
         <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
         <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1903,7 +1903,7 @@
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="P13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="AC13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2129,31 +2129,31 @@
         <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
         <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.4</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>3.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2334,40 +2334,40 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
         <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
         <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2376,22 +2376,22 @@
         <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.14</v>
+        <v>2.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="M19" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.51</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>2.27</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3289,16 +3289,16 @@
         <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="T24" t="n">
         <v>3.5</v>
@@ -3313,7 +3313,7 @@
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
         <v>1.46</v>
@@ -3328,7 +3328,7 @@
         <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
         <v>1.12</v>
@@ -3340,7 +3340,7 @@
         <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
         <v>1.4</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3524,28 +3524,28 @@
         <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
@@ -3557,7 +3557,7 @@
         <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
         <v>1.92</v>
@@ -3566,7 +3566,7 @@
         <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AD26" t="n">
         <v>1.25</v>
@@ -3575,13 +3575,13 @@
         <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3667,16 +3667,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
         <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
         <v>2.15</v>
@@ -3688,7 +3688,7 @@
         <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
         <v>1.91</v>
@@ -3697,10 +3697,10 @@
         <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3768,34 +3768,34 @@
         <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
         <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA28" t="n">
         <v>1.7</v>
@@ -3804,22 +3804,22 @@
         <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3872,40 +3872,40 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="M29" t="n">
         <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="O29" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
         <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
@@ -3914,19 +3914,19 @@
         <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
         <v>2.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
         <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>
@@ -3935,10 +3935,10 @@
         <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="M31" t="n">
         <v>3.3</v>
@@ -4134,7 +4134,7 @@
         <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="AA31" t="n">
         <v>1.97</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
@@ -924,13 +924,13 @@
         <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
@@ -939,13 +939,13 @@
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>4.5</v>
@@ -957,13 +957,13 @@
         <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
         <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1254,19 +1254,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1278,7 +1278,7 @@
         <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="U7" t="n">
         <v>1.45</v>
@@ -1299,10 +1299,10 @@
         <v>4.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC7" t="n">
         <v>2.62</v>
@@ -1311,10 +1311,10 @@
         <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.89</v>
+        <v>3.52</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.49</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>5.85</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
         <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2129,28 +2129,28 @@
         <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF14" t="n">
         <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
         <v>1.62</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="M17" t="n">
         <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -2468,49 +2468,49 @@
         <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
         <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
         <v>4.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB18" t="n">
         <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -2706,31 +2706,31 @@
         <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
         <v>2.43</v>
@@ -2739,16 +2739,16 @@
         <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
         <v>2.95</v>
@@ -2816,7 +2816,7 @@
         <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.38</v>
@@ -2825,7 +2825,7 @@
         <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
         <v>1.36</v>
@@ -2840,13 +2840,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
         <v>1.8</v>
@@ -2858,13 +2858,13 @@
         <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
         <v>1.47</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.16</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
@@ -2944,7 +2944,7 @@
         <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
         <v>1.58</v>
@@ -2956,37 +2956,37 @@
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3042,70 +3042,70 @@
         <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="T22" t="n">
         <v>3.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
         <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
         <v>3.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
         <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3158,19 +3158,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="O23" t="n">
         <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
         <v>2.6</v>
@@ -3182,16 +3182,16 @@
         <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.08</v>
@@ -3200,13 +3200,13 @@
         <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>4</v>
@@ -3215,16 +3215,16 @@
         <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
         <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3441,10 +3441,10 @@
         <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.81</v>
       </c>
       <c r="N29" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.17</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4000,13 +4000,13 @@
         <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="P30" t="n">
         <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
@@ -4018,13 +4018,13 @@
         <v>3.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
         <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
@@ -4244,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
         <v>1.42</v>
@@ -4253,16 +4253,16 @@
         <v>2.65</v>
       </c>
       <c r="T32" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
@@ -4286,7 +4286,7 @@
         <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
         <v>1.85</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -668,25 +668,25 @@
         <v>2.17</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -698,34 +698,34 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45985.375</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="O3" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
@@ -796,37 +796,37 @@
         <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
         <v>3.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC3" t="n">
         <v>3.72</v>
@@ -835,13 +835,13 @@
         <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
         <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
         <v>1.3</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>4.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>3.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.89</v>
+        <v>2.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.55</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>3.98</v>
+        <v>3.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.84</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
         <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
         <v>2.08</v>
@@ -1391,7 +1391,7 @@
         <v>5.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
         <v>2.73</v>
@@ -1400,22 +1400,22 @@
         <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
         <v>6</v>
       </c>
       <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="AA8" t="n">
         <v>1.98</v>
@@ -1427,7 +1427,7 @@
         <v>3.52</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
         <v>1.85</v>
@@ -1439,7 +1439,7 @@
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1614,52 +1614,52 @@
         <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
         <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
         <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
         <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
         <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AA10" t="n">
         <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
         <v>2.89</v>
@@ -1668,16 +1668,16 @@
         <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.3</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>3.53</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1864,10 +1864,10 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
         <v>2.47</v>
@@ -1882,7 +1882,7 @@
         <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.08</v>
@@ -1894,10 +1894,10 @@
         <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
         <v>4.2</v>
@@ -1906,7 +1906,7 @@
         <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
         <v>1.85</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
         <v>3.3</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
         <v>1.12</v>
@@ -2251,28 +2251,28 @@
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
         <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
         <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
         <v>2.09</v>
@@ -2343,22 +2343,22 @@
         <v>3.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
@@ -2367,31 +2367,31 @@
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
         <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.4</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AB18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.37</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.36</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.88</v>
       </c>
-      <c r="N22" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.85</v>
+        <v>2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.68</v>
+        <v>3.92</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S24" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,49 +3396,49 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
         <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
         <v>2.5</v>
@@ -3447,22 +3447,22 @@
         <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>4.01</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
         <v>3.1</v>
@@ -3545,40 +3545,40 @@
         <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.73</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,49 +3634,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
         <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
         <v>2.15</v>
@@ -3685,19 +3685,19 @@
         <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
         <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
         <v>1.73</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="M29" t="n">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="P31" t="n">
         <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
@@ -4140,22 +4140,22 @@
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
         <v>3.22</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
@@ -4173,10 +4173,10 @@
         <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="M3" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.43</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.27</v>
+        <v>2.94</v>
       </c>
       <c r="M4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.05</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.32</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
         <v>1.12</v>
@@ -2013,28 +2013,28 @@
         <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
         <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
         <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>2.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.4</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.25</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.67</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.73</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AD21" t="n">
         <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC22" t="n">
         <v>3.85</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,49 +3158,49 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
         <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
         <v>2.5</v>
@@ -3209,22 +3209,22 @@
         <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="M24" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.59</v>
+        <v>3.85</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="O25" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="T25" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="P26" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
         <v>3.1</v>
@@ -3545,40 +3545,40 @@
         <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
         <v>1.73</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,28 +3634,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="O27" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
         <v>3.1</v>
@@ -3664,40 +3664,40 @@
         <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
         <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
         <v>1.73</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q30" t="n">
         <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
         <v>3.04</v>
@@ -4021,43 +4021,43 @@
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W30" t="n">
         <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45985.79166666666</v>
@@ -4229,31 +4229,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="T32" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
@@ -4262,34 +4262,34 @@
         <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AD32" t="n">
         <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
         <v>1.33</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="O2" t="n">
         <v>5.91</v>
@@ -689,13 +689,13 @@
         <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
         <v>1.3</v>
@@ -704,10 +704,10 @@
         <v>2.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
         <v>3.42</v>
@@ -722,7 +722,7 @@
         <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH2" t="n">
         <v>1.09</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.27</v>
+        <v>2.94</v>
       </c>
       <c r="M3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.05</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.32</v>
       </c>
-      <c r="V3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="M4" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.43</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.3</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1864,25 +1864,25 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
         <v>8.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.08</v>
@@ -1891,31 +1891,31 @@
         <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
         <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.1</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.04</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.12</v>
@@ -2013,28 +2013,28 @@
         <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
         <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
         <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.8</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AD17" t="n">
         <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4.84</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.36</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.88</v>
       </c>
-      <c r="N22" t="n">
-        <v>3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3322,10 +3322,10 @@
         <v>2.37</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="N25" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
         <v>8.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
         <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,28 +3634,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="P27" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
         <v>3.1</v>
@@ -3664,40 +3664,40 @@
         <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
         <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
         <v>1.73</v>
@@ -3753,61 +3753,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
         <v>2.97</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
         <v>1.85</v>
@@ -3816,7 +3816,7 @@
         <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
         <v>1.75</v>
@@ -3991,43 +3991,43 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O30" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="P30" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
         <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="T30" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V30" t="n">
         <v>7.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
         <v>1.32</v>
@@ -4036,25 +4036,25 @@
         <v>2.89</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
         <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
         <v>2.2</v>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
         <v>3</v>
@@ -4122,16 +4122,16 @@
         <v>2.46</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
         <v>2.81</v>
@@ -4140,10 +4140,10 @@
         <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.05</v>
@@ -4161,10 +4161,10 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE31" t="n">
         <v>1.73</v>
@@ -4173,7 +4173,7 @@
         <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
         <v>1.6</v>
@@ -4229,49 +4229,49 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
         <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
         <v>2.59</v>
       </c>
       <c r="T32" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V32" t="n">
         <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
         <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
         <v>2.12</v>
@@ -4280,22 +4280,22 @@
         <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="M3" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.43</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="P5" t="n">
         <v>1.77</v>
@@ -1037,7 +1037,7 @@
         <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>3.98</v>
@@ -1046,7 +1046,7 @@
         <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>11.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1055,16 +1055,16 @@
         <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
         <v>5.7</v>
@@ -1073,10 +1073,10 @@
         <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
         <v>1.41</v>
@@ -1254,19 +1254,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.17</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
@@ -1284,7 +1284,7 @@
         <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1293,16 +1293,16 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
         <v>2.62</v>
@@ -1311,16 +1311,16 @@
         <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.62</v>
+        <v>3.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.89</v>
+        <v>3.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>6.3</v>
+        <v>6.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1894,10 +1894,10 @@
         <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
         <v>4.4</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>4.25</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.31</v>
@@ -1992,31 +1992,31 @@
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
         <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
         <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
         <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
         <v>2.56</v>
@@ -2028,13 +2028,13 @@
         <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
         <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
         <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
         <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
         <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="P18" t="n">
         <v>2.15</v>
@@ -2581,43 +2581,43 @@
         <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
         <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
         <v>1.66</v>
@@ -2626,10 +2626,10 @@
         <v>1.96</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.44</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.84</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.37</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.58</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>4.84</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AB21" t="n">
         <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.59</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.88</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AA23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
         <v>2.7</v>
@@ -3560,10 +3560,10 @@
         <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>4.4</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z28" t="n">
         <v>3.9</v>
       </c>
-      <c r="O28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.81</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.72</v>
+        <v>3.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -668,40 +668,40 @@
         <v>1.6</v>
       </c>
       <c r="O2" t="n">
-        <v>5.91</v>
+        <v>5.84</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -710,22 +710,22 @@
         <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45985.375</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
         <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -909,7 +909,7 @@
         <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>2.8</v>
@@ -921,7 +921,7 @@
         <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
@@ -939,7 +939,7 @@
         <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AA4" t="n">
         <v>2.4</v>
@@ -951,19 +951,19 @@
         <v>3.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1025,28 +1025,28 @@
         <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>11.5</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1067,22 +1067,22 @@
         <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.7</v>
+        <v>6.04</v>
       </c>
       <c r="AD5" t="n">
         <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
         <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1135,70 +1135,70 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
         <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.06</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.5</v>
+        <v>4.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
         <v>1.36</v>
@@ -1263,22 +1263,22 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
         <v>1.45</v>
@@ -1287,16 +1287,16 @@
         <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>4.06</v>
       </c>
       <c r="AA7" t="n">
         <v>1.63</v>
@@ -1308,7 +1308,7 @@
         <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
         <v>1.74</v>
@@ -1317,10 +1317,10 @@
         <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>6.3</v>
+        <v>6.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O9" t="n">
         <v>2.25</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="P9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.12</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.34</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG10" t="n">
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
         <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.8</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
         <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1864,22 +1864,22 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -1906,16 +1906,16 @@
         <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AF12" t="n">
         <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.31</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.4</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.96</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
         <v>5</v>
@@ -2242,7 +2242,7 @@
         <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.2</v>
@@ -2251,28 +2251,28 @@
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2340,22 +2340,22 @@
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2364,10 +2364,10 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
         <v>1.91</v>
@@ -2376,22 +2376,22 @@
         <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
         <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,31 +2444,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="O17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.43</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
         <v>1.51</v>
@@ -2477,40 +2477,40 @@
         <v>5.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.45</v>
+        <v>4.73</v>
       </c>
       <c r="AA17" t="n">
         <v>1.62</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2572,40 +2572,40 @@
         <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="P18" t="n">
         <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
         <v>1.9</v>
@@ -2617,19 +2617,19 @@
         <v>3.35</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
         <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
         <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="P20" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4.84</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.36</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG20" t="n">
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
         <v>4.9</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.75</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
         <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.59</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="P22" t="n">
         <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
         <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
         <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
         <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.79</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,49 +3634,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
         <v>2.15</v>
@@ -3685,22 +3685,22 @@
         <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
         <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.28</v>
+        <v>2.73</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.36</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.22</v>
-      </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.72</v>
+        <v>3.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.35</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.56</v>
-      </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.97</v>
+        <v>4.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.88</v>
+        <v>2.72</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3991,19 +3991,19 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
         <v>2.15</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="Q30" t="n">
         <v>5.5</v>
@@ -4012,49 +4012,49 @@
         <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="T30" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
         <v>2.2</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>2.92</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
         <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.88</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3</v>
-      </c>
       <c r="AA32" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AF32" t="n">
         <v>1.94</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45985.875</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.91</v>
+        <v>4.06</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.65</v>
+        <v>2.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.04</v>
+        <v>4.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O6" t="n">
-        <v>4.06</v>
+        <v>2.91</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.89</v>
+        <v>4.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.07</v>
+        <v>6.04</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
         <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6.65</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AD8" t="n">
         <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="U9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.39</v>
+        <v>4.09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.52</v>
+        <v>3.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="M11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.44</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.73</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
         <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
         <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
         <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
         <v>1.49</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
         <v>1.58</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
         <v>2.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>2.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.3</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.6</v>
+        <v>4.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.82</v>
+        <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="O24" t="n">
-        <v>3.12</v>
+        <v>4.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W24" t="n">
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
         <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3753,16 +3753,16 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="O28" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -3771,7 +3771,7 @@
         <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
         <v>2.56</v>
@@ -3780,16 +3780,16 @@
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
         <v>8.6</v>
       </c>
       <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
@@ -3807,16 +3807,16 @@
         <v>3.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
         <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.75</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>2.08</v>
       </c>
       <c r="O4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.44</v>
+        <v>2.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.78</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.65</v>
+        <v>6.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.09</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
         <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>2.71</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>6.3</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="AD10" t="n">
         <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.01</v>
+        <v>2.35</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>6.35</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
         <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.26</v>
+        <v>2.81</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="M18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.2</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>2.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,37 +2682,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="P19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.12</v>
@@ -2721,34 +2721,34 @@
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC19" t="n">
         <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
         <v>2.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,40 +2801,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>2.48</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.63</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
@@ -2843,31 +2843,31 @@
         <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
         <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.9</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V24" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.82</v>
+        <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="M25" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O25" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.97</v>
+        <v>4.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.88</v>
+        <v>2.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.72</v>
+        <v>3.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4110,19 +4110,19 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O31" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="P31" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
         <v>3.85</v>
@@ -4134,7 +4134,7 @@
         <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
@@ -4146,25 +4146,25 @@
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE31" t="n">
         <v>1.73</v>
@@ -4173,10 +4173,10 @@
         <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
         <v>3.3</v>
@@ -817,16 +817,16 @@
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC3" t="n">
         <v>4.5</v>
@@ -838,13 +838,13 @@
         <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="O5" t="n">
-        <v>4.06</v>
+        <v>2.92</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89</v>
+        <v>4.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>3.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.07</v>
+        <v>5.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.3</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.91</v>
+        <v>4.06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.65</v>
+        <v>2.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.04</v>
+        <v>4.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
         <v>4.5</v>
@@ -1394,52 +1394,52 @@
         <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
         <v>2.81</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V9" t="n">
-        <v>6.35</v>
+        <v>6.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.01</v>
       </c>
       <c r="AD10" t="n">
         <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1739,64 +1739,64 @@
         <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
         <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
         <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
         <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
         <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1870,13 +1870,13 @@
         <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
         <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
         <v>9.5</v>
@@ -1885,22 +1885,22 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
         <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD12" t="n">
         <v>1.2</v>
@@ -1909,13 +1909,13 @@
         <v>1.96</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1971,70 +1971,70 @@
         <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.18</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.31</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.21</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,46 +2206,46 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.08</v>
+        <v>3.89</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
         <v>4.2</v>
@@ -2254,25 +2254,25 @@
         <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.2</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.35</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="AA18" t="n">
         <v>1.61</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.78</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC20" t="n">
         <v>3.35</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="R22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V22" t="n">
+        <v>10</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="Z22" t="n">
         <v>2.4</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>4.4</v>
+        <v>3.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AA24" t="n">
         <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2.9</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AA25" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3634,31 +3634,31 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
         <v>4.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="T27" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="U27" t="n">
         <v>1.33</v>
@@ -3676,13 +3676,13 @@
         <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>4.4</v>
@@ -3691,16 +3691,16 @@
         <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.72</v>
+        <v>3.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.97</v>
+        <v>4.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.88</v>
+        <v>2.72</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -642,90 +642,90 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>5.84</v>
+        <v>4.99</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AA2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.93</v>
       </c>
       <c r="AF2" t="n">
         <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45985.375</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="O3" t="n">
         <v>2.95</v>
@@ -817,16 +817,16 @@
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>4.5</v>
@@ -906,28 +906,28 @@
         <v>2.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -936,10 +936,10 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
         <v>2.4</v>
@@ -948,19 +948,19 @@
         <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AF4" t="n">
         <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
         <v>1.3</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>2.92</v>
@@ -1055,16 +1055,16 @@
         <v>1.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
         <v>5.9</v>
@@ -1144,28 +1144,28 @@
         <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.06</v>
+        <v>3.96</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
@@ -1174,10 +1174,10 @@
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
         <v>2.05</v>
@@ -1186,7 +1186,7 @@
         <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
         <v>1.22</v>
@@ -1198,10 +1198,10 @@
         <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1263,40 +1263,40 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
         <v>5.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
         <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="AA7" t="n">
         <v>1.63</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
         <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.95</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>2.47</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1894,10 +1894,10 @@
         <v>2.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
         <v>4.33</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.14</v>
+        <v>3.89</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2102,13 +2102,13 @@
         <v>2.13</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
         <v>2.85</v>
@@ -2123,10 +2123,10 @@
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
         <v>3.18</v>
@@ -2138,10 +2138,10 @@
         <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.75</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.89</v>
+        <v>3.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
         <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2334,25 +2334,25 @@
         <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P16" t="n">
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>7.5</v>
@@ -2361,10 +2361,10 @@
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
         <v>3.25</v>
@@ -2376,13 +2376,13 @@
         <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
         <v>1.95</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="AA17" t="n">
         <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.78</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
@@ -2605,31 +2605,31 @@
         <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,37 +2682,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
         <v>1.12</v>
@@ -2721,34 +2721,34 @@
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
         <v>2.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2810,40 +2810,40 @@
         <v>2.95</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
         <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA20" t="n">
         <v>1.9</v>
@@ -2852,22 +2852,22 @@
         <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="P21" t="n">
-        <v>2.53</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.36</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.37</v>
       </c>
       <c r="AG21" t="n">
         <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="T22" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U22" t="n">
         <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
         <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.28</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
         <v>3.4</v>
@@ -3322,10 +3322,10 @@
         <v>2.37</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>3.52</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.74</v>
+        <v>3.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V25" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.82</v>
+        <v>4.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>3.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="O27" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
         <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="O28" t="n">
         <v>2.63</v>
@@ -3771,16 +3771,16 @@
         <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
         <v>8.6</v>
@@ -3789,16 +3789,16 @@
         <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
         <v>1.67</v>
@@ -3813,13 +3813,13 @@
         <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3893,28 +3893,28 @@
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="T29" t="n">
         <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA29" t="n">
         <v>1.7</v>
@@ -3926,7 +3926,7 @@
         <v>2.72</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE29" t="n">
         <v>1.73</v>
@@ -3938,7 +3938,7 @@
         <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>
@@ -4000,16 +4000,16 @@
         <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="P30" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
         <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
         <v>2.59</v>
@@ -4021,7 +4021,7 @@
         <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="W30" t="n">
         <v>1.02</v>
@@ -4045,10 +4045,10 @@
         <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF30" t="n">
         <v>1.73</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="M31" t="n">
         <v>3.35</v>
@@ -4119,22 +4119,22 @@
         <v>3.15</v>
       </c>
       <c r="O31" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
         <v>3.85</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
         <v>1.38</v>
@@ -4146,7 +4146,7 @@
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
         <v>1.25</v>
@@ -4161,7 +4161,7 @@
         <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AD31" t="n">
         <v>1.34</v>
@@ -4176,7 +4176,7 @@
         <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45985.83333333334</v>
@@ -4238,19 +4238,19 @@
         <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
         <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
         <v>3.15</v>
@@ -4271,7 +4271,7 @@
         <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA32" t="n">
         <v>2</v>
@@ -4280,19 +4280,19 @@
         <v>1.72</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.86</v>
+        <v>4.35</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
         <v>1.94</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH32" t="n">
         <v>1.67</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
         <v>3.3</v>
@@ -808,7 +808,7 @@
         <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -817,25 +817,25 @@
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
         <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
         <v>1.7</v>
@@ -844,7 +844,7 @@
         <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
         <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -939,31 +939,31 @@
         <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
         <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.55</v>
+        <v>2.93</v>
       </c>
       <c r="R5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.65</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>4.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.96</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45985.54166666666</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="O7" t="n">
         <v>2.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
         <v>5.7</v>
@@ -1293,34 +1293,34 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45985.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.76</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
         <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.45</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.48</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
         <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
         <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
         <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AG10" t="n">
         <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.35</v>
       </c>
-      <c r="N11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>6.3</v>
+        <v>6.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
         <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1864,58 +1864,58 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T12" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
         <v>9.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45985.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.89</v>
+        <v>3.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.04</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>2.7</v>
@@ -2221,58 +2221,58 @@
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.14</v>
+        <v>3.86</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="O16" t="n">
         <v>3.45</v>
@@ -2340,19 +2340,19 @@
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>7.5</v>
@@ -2364,34 +2364,34 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>3.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
         <v>1.95</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45985.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
@@ -2486,31 +2486,31 @@
         <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.7</v>
+        <v>4.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="O19" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
         <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.34</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45985.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="O22" t="n">
-        <v>3.12</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="W22" t="n">
         <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
         <v>3.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45985.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.45</v>
+        <v>3.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45985.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
         <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="AA24" t="n">
         <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45985.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="M25" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="O25" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45985.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,64 +3634,64 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE27" t="n">
         <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
         <v>1.85</v>
@@ -3700,7 +3700,7 @@
         <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45985.69791666666</v>
@@ -3753,19 +3753,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="N28" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
         <v>3.9</v>
@@ -3774,34 +3774,34 @@
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="T28" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>3.88</v>
@@ -3810,16 +3810,16 @@
         <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45985.70833333334</v>
@@ -3872,43 +3872,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="O29" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
         <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
         <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
         <v>1.22</v>
@@ -3917,28 +3917,28 @@
         <v>3.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD29" t="n">
         <v>1.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
         <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45985.70833333334</v>

--- a/jogos_2025-11-24.xlsx
+++ b/jogos_2025-11-24.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,19 +752,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC3" t="n">
         <v>3.72</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V3" t="n">
-        <v>9</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45985.52083333334</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,19 +871,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,77 +893,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.64</v>
+        <v>3.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45985.52083333334</v>
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1121,17 +1121,17 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1240,17 +1240,17 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2.01</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
         <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
         <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1594,20 +1594,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.39</v>
+        <v>1.84</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="P11" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45985.58333333334</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45985.625</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.89</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T14" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
         <v>5.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB14" t="n">
         <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45985.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45985.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,43 +2444,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O17" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.7</v>
+        <v>3.59</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
         <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.15</v>
@@ -2489,28 +2489,28 @@
         <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.4</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>5.52</v>
       </c>
       <c r="O18" t="n">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.63</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4.64</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.78</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
         <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45985.66666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.2</v>
+      </